--- a/data/trans_orig/cron_mort_index-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la mortalidad</t>
+          <t>Índice de cronicidad física en base a la mortalidad (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,05; 0,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,28</t>
+          <t>0,17; 0,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,12</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,08</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,22 +866,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,27</t>
+          <t>0,18; 0,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,12</t>
+          <t>0,07; 0,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,15</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,17</t>
+          <t>0,09; 0,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,11</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,31</t>
+          <t>0,23; 0,31</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,18</t>
+          <t>0,1; 0,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,57</t>
+          <t>0,18; 0,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,49</t>
+          <t>0,21; 0,48</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,17</t>
+          <t>0,08; 0,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,15; 0,27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0,12; 0,29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,11</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,17</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>0,15; 0,26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,14</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,11; 0,28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,1</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,17</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,12</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 0,26</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,39</t>
+          <t>0,28; 0,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,16</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,32</t>
+          <t>0,23; 0,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,06</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,11</t>
+          <t>0,07; 0,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,15</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,3</t>
+          <t>0,21; 0,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,24</t>
+          <t>0,07; 0,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,09; 0,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,22</t>
+          <t>0,07; 0,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,11; 0,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_mort_index-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Provincia-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -721,47 +721,47 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,13</t>
+          <t>0,05; 0,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,05; 0,12</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,18; 0,28</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,02; 0,07</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,13</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>0,05; 0,11</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 0,29</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,07</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,14</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,11</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,22</t>
+          <t>0,14; 0,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,06</t>
+          <t>0,02; 0,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,24</t>
+          <t>0,16; 0,23</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,22 +866,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,28</t>
+          <t>0,17; 0,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,11</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,15</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,18; 0,24</t>
         </is>
       </c>
     </row>
@@ -996,19 +996,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,03; 0,08</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,17</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>0,04; 0,09</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,04; 0,09</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>0,22; 0,33</t>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,17</t>
+          <t>0,09; 0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,15</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,07; 0,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,31</t>
+          <t>0,23; 0,3</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,17</t>
+          <t>0,1; 0,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,33</t>
+          <t>0,19; 0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,58</t>
+          <t>0,17; 0,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,48</t>
+          <t>0,19; 0,26</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,27 +1243,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0,13</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>0,22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,18</t>
+          <t>0,07; 0,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,27</t>
+          <t>0,15; 0,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,29</t>
+          <t>0,21; 0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,11</t>
+          <t>0,05; 0,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,26</t>
+          <t>0,19; 0,26</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,08; 0,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,32</t>
+          <t>0,23; 0,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1503,47 +1503,47 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,25</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,12</t>
+          <t>0,07; 0,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,15</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,3</t>
+          <t>0,22; 0,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,24</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,06; 0,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,12</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,14</t>
+          <t>0,1; 0,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,25</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,27 +1663,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>0,19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
         </is>
       </c>
     </row>
@@ -1701,17 +1701,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,05; 0,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,13</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,22</t>
+          <t>0,17; 0,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,22</t>
+          <t>0,16; 0,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,2</t>
+          <t>0,17; 0,22</t>
         </is>
       </c>
     </row>
@@ -1783,47 +1783,47 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0,22</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,25</t>
+          <t>0,22; 0,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,2; 0,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,22; 0,24</t>
         </is>
       </c>
     </row>
